--- a/data/quarters/synthetic/2027Q2/SYNTHETIC_portfolio_Q2_2027.xlsx
+++ b/data/quarters/synthetic/2027Q2/SYNTHETIC_portfolio_Q2_2027.xlsx
@@ -1150,7 +1150,7 @@
         <v>43666</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>46407</v>
+        <v>46328</v>
       </c>
       <c r="H9" s="13" t="n">
         <v>65</v>
@@ -1730,7 +1730,7 @@
         <v>43895</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>44477</v>
+        <v>46245</v>
       </c>
       <c r="H17" s="13" t="n">
         <v>176.3</v>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Acquired</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
@@ -6984,7 +6984,7 @@
         <v>0.058</v>
       </c>
       <c r="K89" s="13" t="n">
-        <v>0</v>
+        <v>48.8</v>
       </c>
       <c r="L89" s="13" t="n">
         <v>0</v>
@@ -6993,16 +6993,28 @@
         <f>(K89+L89)/I89</f>
         <v/>
       </c>
-      <c r="N89" s="13" t="n"/>
-      <c r="O89" s="6" t="n"/>
-      <c r="P89" s="6" t="n"/>
-      <c r="Q89" s="16" t="n"/>
-      <c r="R89" s="13" t="n"/>
+      <c r="N89" s="13" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="O89" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="P89" s="6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="Q89" s="16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="R89" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="S89" s="17">
         <f>IF(AND(ISNUMBER(Q89),Q89&gt;0),R89/Q89,"-")</f>
         <v/>
       </c>
-      <c r="T89" s="9" t="n"/>
+      <c r="T89" s="9" t="n">
+        <v>495</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8925,7 +8937,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>hc-valuation engine 0.1.0, policy 2026Q4-0.1, run b9e1bcc61c42</t>
+          <t>hc-valuation engine 0.1.0, policy 2026Q4-0.1, run df62f01d0864</t>
         </is>
       </c>
     </row>
@@ -8992,7 +9004,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>hc-valuation engine 0.1.0, policy 2027Q1-0.1, run 28c1475c6d04</t>
+          <t>hc-valuation engine 0.1.0, policy 2027Q1-0.1, run 8cefe0cb2697</t>
         </is>
       </c>
     </row>
@@ -9266,16 +9278,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Redgrove Health</t>
+          <t>Knollward</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>term_sheet</t>
+          <t>unconfirmed_exit</t>
         </is>
       </c>
       <c r="C6" s="19" t="n">
-        <v>46461</v>
+        <v>46438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -9284,11 +9296,11 @@
       </c>
       <c r="E6" s="19" t="n"/>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Signed the morning of the close.</t>
+          <t>exit closed 2027-02-20 at $30.0M with no cash recorded; record the closing with its proceeds when the cash arrives, or write the position to zero</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -9311,7 +9323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9393,10 +9405,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Knollward</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Exit recorded as Acquired in the quarter with no cash received; the committee held $48.80M rather than writing the position off, so it rolls forward as Active at that value with an 'unconfirmed exit' open item. Record the closing with its proceeds when the cash arrives, or write it to zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pellagrin</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>same-terms extension on 2026-08-11 is not price discovery; the staleness clock runs from 2021-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Foxtrellis</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>same-terms extension on 2027-02-10 is not price discovery; the staleness clock runs from 2023-10-14</t>
         </is>
